--- a/docs/Example Files/CRYSS V2.0 Input File Templates/4 Component Mixture.xlsx
+++ b/docs/Example Files/CRYSS V2.0 Input File Templates/4 Component Mixture.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\06 website\idiocratease-iggy.github.io\docs\Example Files\CRYSS V2.0 Input File Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00113552-BAB5-4D6E-89D8-0C954E58C2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862B4809-01D0-4739-AA17-0746677CB94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24345" yWindow="525" windowWidth="31545" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2964" yWindow="348" windowWidth="31980" windowHeight="16116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="slice_records" sheetId="1" r:id="rId1"/>
+    <sheet name="CRYSS Input File V2.0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -247,18 +247,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -268,6 +256,21 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -275,9 +278,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,47 +583,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="19" width="12.5703125" customWidth="1"/>
+    <col min="15" max="19" width="12.5546875" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="12" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="9" t="s">
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="16" t="s">
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="19"/>
       <c r="U1" s="1"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -662,27 +662,27 @@
       <c r="M2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="11" t="s">
         <v>14</v>
       </c>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -703,7 +703,7 @@
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -724,7 +724,7 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -745,7 +745,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -766,7 +766,7 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -787,7 +787,7 @@
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -808,7 +808,7 @@
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -829,7 +829,7 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -850,7 +850,7 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -871,7 +871,7 @@
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -892,7 +892,7 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -913,7 +913,7 @@
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -934,7 +934,7 @@
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -955,7 +955,7 @@
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -976,7 +976,7 @@
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -997,7 +997,7 @@
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -1018,7 +1018,7 @@
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1039,7 +1039,7 @@
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -1060,7 +1060,7 @@
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1081,7 +1081,7 @@
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -1102,7 +1102,7 @@
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -1123,7 +1123,7 @@
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
